--- a/data/trans_orig/P5_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29877</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23866</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44915</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>63618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61442</t>
+          <t>61570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64598</t>
+          <t>64659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102218</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122108</t>
+          <t>122868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41496</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61294</t>
+          <t>61406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51186</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78689</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106704</t>
+          <t>105774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125952</t>
+          <t>125840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145750</t>
+          <t>144878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137545</t>
+          <t>138321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155646</t>
+          <t>155739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269273</t>
+          <t>270203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>297288</t>
+          <t>295807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32186</t>
+          <t>32164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47758</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>69293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54293</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67437</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63055</t>
+          <t>62926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78492</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121124</t>
+          <t>120447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>142127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>51582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52391</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72166</t>
+          <t>73675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>98563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99663</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117809</t>
+          <t>118042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95703</t>
+          <t>96048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114192</t>
+          <t>113142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201544</t>
+          <t>200606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227003</t>
+          <t>225494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125887</t>
+          <t>124435</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158034</t>
+          <t>156383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264926</t>
+          <t>265693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311705</t>
+          <t>313158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>346976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377472</t>
+          <t>378924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397745</t>
+          <t>395653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>718750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766982</t>
+          <t>766215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31562</t>
+          <t>30579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>46783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>36853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53219</t>
+          <t>54349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72782</t>
+          <t>71572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96008</t>
+          <t>95901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56024</t>
+          <t>57338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72559</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120155</t>
+          <t>120262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143381</t>
+          <t>144591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86779</t>
+          <t>86521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115480</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146356</t>
+          <t>146322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94974</t>
+          <t>94947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114490</t>
+          <t>115194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>106703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129754</t>
+          <t>128711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206212</t>
+          <t>206246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237088</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>29296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45145</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59902</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82617</t>
+          <t>82390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52835</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>58991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74238</t>
+          <t>74937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117176</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139891</t>
+          <t>139404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60594</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42143</t>
+          <t>42383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>60656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>90836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116044</t>
+          <t>115709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54926</t>
+          <t>55114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73028</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71086</t>
+          <t>71046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89559</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131177</t>
+          <t>131512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157221</t>
+          <t>156385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186550</t>
+          <t>189494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224109</t>
+          <t>224900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>360875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>412380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277346</t>
+          <t>277165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314672</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352231</t>
+          <t>349287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603074</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>653497</t>
+          <t>654871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>25455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76510</t>
+          <t>75928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62390</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77466</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>56837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>72812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124461</t>
+          <t>125043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146213</t>
+          <t>145666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44402</t>
+          <t>46317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>65286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>63591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85604</t>
+          <t>86525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115292</t>
+          <t>114478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145266</t>
+          <t>143508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92382</t>
+          <t>90979</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111863</t>
+          <t>109948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124988</t>
+          <t>124067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>146732</t>
+          <t>147001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221591</t>
+          <t>223349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>251565</t>
+          <t>252379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63143</t>
+          <t>63391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43867</t>
+          <t>43806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92070</t>
+          <t>92677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117892</t>
+          <t>120445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81171</t>
+          <t>80923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101022</t>
+          <t>99448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158593</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184415</t>
+          <t>183808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33449</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51400</t>
+          <t>52986</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>62552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82815</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108909</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87490</t>
+          <t>86177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>67452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85518</t>
+          <t>86249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142034</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168128</t>
+          <t>168918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166203</t>
+          <t>166664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201377</t>
+          <t>201612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193596</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>232148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369934</t>
+          <t>371768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>423452</t>
+          <t>424218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322846</t>
+          <t>322611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358020</t>
+          <t>357559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339659</t>
+          <t>338885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>377437</t>
+          <t>374790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671804</t>
+          <t>671038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>725322</t>
+          <t>723488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>48745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>48085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103596</t>
+          <t>104023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>27621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>45188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>32124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>51185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64578</t>
+          <t>63032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112520</t>
+          <t>112694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130079</t>
+          <t>130261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>131369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151032</t>
+          <t>150430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249998</t>
+          <t>250235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275859</t>
+          <t>277405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29299</t>
+          <t>29795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50568</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57250</t>
+          <t>56789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86269</t>
+          <t>84183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133028</t>
+          <t>133735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151158</t>
+          <t>150738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160979</t>
+          <t>160987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182248</t>
+          <t>181752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299165</t>
+          <t>301251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328184</t>
+          <t>328645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126399</t>
+          <t>125659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56110</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75055</t>
+          <t>74142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177920</t>
+          <t>179856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149059</t>
+          <t>149799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>241119</t>
+          <t>240482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249373</t>
+          <t>251038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273651</t>
+          <t>274590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>403020</t>
+          <t>401084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>505885</t>
+          <t>506798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113404</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>213673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149274</t>
+          <t>151459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>237586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>342996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>459514</t>
+          <t>451065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551334</t>
+          <t>553012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>611754</t>
+          <t>609569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>650407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1076971</t>
+          <t>1082771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1186447</t>
+          <t>1188181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23490</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38079</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22983</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16989</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30030</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17641</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29903</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23805</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38033</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63618</t>
+          <t>63869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57777</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50385</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64974</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55576</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48529</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61570</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48656</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60918</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>70,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57777</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50431</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64659</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103405</t>
+          <t>103154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122868</t>
+          <t>122473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41681</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32770</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>51887</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51203</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>42368</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>61406</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>41706</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61890</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41681</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>32992</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80170</t>
+          <t>77237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105774</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>147050</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>136844</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>155961</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>136043</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>125840</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>144878</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>125356</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>145540</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>147050</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>138321</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>155739</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>270203</t>
+          <t>269768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>295807</t>
+          <t>298740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32333</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25207</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40239</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25209</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18447</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32164</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18298</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32550</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>32333</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25100</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40335</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47613</t>
+          <t>47948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69293</t>
+          <t>67957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70928</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63022</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78054</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61270</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54315</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68032</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53929</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>68181</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70928</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>62926</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78161</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120447</t>
+          <t>121783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142127</t>
+          <t>141792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42946</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34552</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42060</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33033</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51582</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>32667</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50897</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42946</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34952</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52046</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98563</t>
+          <t>97779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105148</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95968</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>113542</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>109015</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99493</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118042</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>100178</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>118408</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105148</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96048</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>113142</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>201390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225494</t>
+          <t>226685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>131055</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>164091</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>156383</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>126371</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>157231</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>132896</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>166042</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265693</t>
+          <t>265826</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313158</t>
+          <t>312670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>380902</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>364458</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>397494</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>68,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>75,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>361904</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346976</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>378924</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>346128</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>376988</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>71,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>380902</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>362507</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>395653</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>718750</t>
+          <t>719238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766215</t>
+          <t>766082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44905</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35932</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53440</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39185</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30579</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46783</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32144</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47580</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>44905</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36853</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>54349</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71572</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95901</t>
+          <t>97575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67138</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58603</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76111</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>59,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>64936</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57338</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73542</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56541</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>71977</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67138</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57694</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75190</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120262</t>
+          <t>118588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144591</t>
+          <t>142214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64515</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86655</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54313</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44150</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>64397</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>45129</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>64912</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>75605</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>64513</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86521</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116428</t>
+          <t>114937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146322</t>
+          <t>146510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>117619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106569</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>128709</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105031</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94947</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115194</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>94432</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>114215</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>117619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106703</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>128711</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206246</t>
+          <t>206058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236140</t>
+          <t>237631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26403</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42307</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36546</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29296</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44786</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28582</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44738</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34331</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>26875</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>42821</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>60947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82390</t>
+          <t>82850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67481</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59505</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75409</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61434</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53194</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68684</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53242</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69398</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67481</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74937</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117403</t>
+          <t>116943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139404</t>
+          <t>138846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51301</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43127</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60670</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51365</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42530</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>60406</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41856</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60283</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51301</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42383</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>60656</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115709</t>
+          <t>116215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80401</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71032</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>88575</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>64155</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>55114</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72990</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>55237</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>73664</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80401</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>71046</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89319</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131512</t>
+          <t>131006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156385</t>
+          <t>156966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>188165</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>225055</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>164635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199800</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>164366</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199035</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>189494</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>224900</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>360875</t>
+          <t>363763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412380</t>
+          <t>411236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>332639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>313726</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>350616</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>295557</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>277165</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>312330</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>277930</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>312599</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>58,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>332639</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>313881</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603366</t>
+          <t>604510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>654871</t>
+          <t>651983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32778</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24507</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40516</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32916</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25990</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40370</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25737</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40619</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32778</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25455</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41430</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55305</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75928</t>
+          <t>76303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65489</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57751</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73760</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69788</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76714</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62085</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76967</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65489</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56837</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72812</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125043</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145666</t>
+          <t>145635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86672</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54278</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>46317</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65286</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>45457</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>64056</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>75308</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>63591</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86525</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114478</t>
+          <t>115600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143508</t>
+          <t>144579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>135284</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>123920</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>146100</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101987</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90979</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109948</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>92209</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>110808</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>135284</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>124067</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>147001</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223349</t>
+          <t>222278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252379</t>
+          <t>251257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52381</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42894</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61717</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>53393</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44866</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63391</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44196</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62590</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>52381</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43806</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62111</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92677</t>
+          <t>92750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120445</t>
+          <t>118800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79790</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70454</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89277</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90921</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80923</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99448</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>81724</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100118</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>63,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79790</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70060</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88365</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156040</t>
+          <t>157685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>183808</t>
+          <t>183735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,107 +5646,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43467</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62523</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42875</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34762</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52986</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>33986</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52087</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>95801</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>83045</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>109929</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>38,18%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>43,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52926</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>43755</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>62552</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>33,66%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>48,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>95801</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>82025</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>109646</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -5759,107 +5759,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>77078</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67481</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86537</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>78064</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>67953</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86177</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68852</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86953</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>71,9%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>155142</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>141014</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>167898</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>61,82%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>56,19%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>77078</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>67452</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>86249</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>66,34%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>155142</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>141297</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>168918</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>120939</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>120939</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>120939</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>195913</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>233758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>166664</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>201612</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>165689</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>201641</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>38,46%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>196243</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>232148</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371768</t>
+          <t>372034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424218</t>
+          <t>420792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>357639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>337275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>375120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>512</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>340761</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322611</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>357559</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322582</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>358534</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>61,54%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>357639</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>338885</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>374790</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671038</t>
+          <t>674464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723488</t>
+          <t>723222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>524223</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5206</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12560</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12728</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8766</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17937</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42231</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37977</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45331</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44783</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39574</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48745</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53060</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48085</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>97843</t>
+          <t>82275</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90349</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104023</t>
+          <t>88093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35430</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27467</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44992</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35793</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27621</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45188</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>76346</t>
+          <t>67753</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63032</t>
+          <t>56742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>80285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122092</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>112530</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>130055</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>122089</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>112694</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130261</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>142001</t>
+          <t>112698</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131369</t>
+          <t>103711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150430</t>
+          <t>119688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>264091</t>
+          <t>234789</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250235</t>
+          <t>222257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>277405</t>
+          <t>245800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>157882</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340437</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>36788</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>47870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,67 +7290,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50560</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>55264</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>83856</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>18,36%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>70059</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>56789</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>84183</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -7363,107 +7363,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162381</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151299</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>170997</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>142665</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133735</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150738</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172710</t>
+          <t>143515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160987</t>
+          <t>134517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181752</t>
+          <t>151668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>81,77%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>76,64%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>305895</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>290830</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>319422</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>81,64%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>315375</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>301251</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>328645</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41019</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30610</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53371</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61326</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34976</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125659</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30893</t>
+          <t>29758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>52184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103770</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74142</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179856</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>251626</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>239274</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>262035</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>214132</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149799</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>240482</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>77,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>263038</t>
+          <t>217293</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>251038</t>
+          <t>204369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274590</t>
+          <t>226795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>477170</t>
+          <t>468919</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401084</t>
+          <t>452177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>506798</t>
+          <t>483782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>105481</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140487</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111726</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>213673</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110621</t>
+          <t>100715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151459</t>
+          <t>134229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237586</t>
+          <t>214098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342996</t>
+          <t>263885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>578328</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>559385</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>594391</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>774</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>523669</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>451065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>553012</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>78,78%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>67,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630810</t>
+          <t>513551</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>609569</t>
+          <t>494953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>650407</t>
+          <t>528467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1154479</t>
+          <t>1091879</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1082771</t>
+          <t>1065169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188181</t>
+          <t>1114956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
